--- a/Output/SelfVsPartnerReport.xlsx
+++ b/Output/SelfVsPartnerReport.xlsx
@@ -362,76 +362,76 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>persuasion_partner</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>ss_psc_more</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>sp_psc_more</t>
-        </is>
-      </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>pressure_partner</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>ss_nsc_more</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>sp_nsc_more</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>pushing_partner</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>ss_push_plan</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>sp_push_plan</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ss_psc_more</t>
+          <t>persuasion_partner</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>[0.18]</t>
+          <t>[0.20]</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.59***</t>
+          <t>0.42***</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.33***</t>
+          <t>0.21***</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.16***</t>
+          <t>0.23***</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.45***</t>
+          <t>0.40***</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.31***</t>
+          <t>0.18***</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>sp_psc_more</t>
+          <t>ss_psc_more</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -441,81 +441,81 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>[0.20]</t>
+          <t>[0.18]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>0.13***</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0.33***</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>0.30***</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0.21***</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0.21***</t>
-        </is>
-      </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.41***</t>
+          <t>0.45***</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ss_nsc_more</t>
+          <t>pressure_partner</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.54***</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.53***</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>[0.51]</t>
+          <t>[0.55]</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.52***</t>
+          <t>0.44***</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.33***</t>
+          <t>0.28***</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.30***</t>
+          <t>0.13***</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>sp_nsc_more</t>
+          <t>ss_nsc_more</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.53***</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.54***</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -525,91 +525,91 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>[0.55]</t>
+          <t>[0.51]</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.17***</t>
+          <t>0.25***</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.37***</t>
+          <t>0.33***</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ss_push_plan</t>
+          <t>pushing_partner</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>0.62***</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t>0.67***</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>0.45**</t>
-        </is>
-      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.55***</t>
+          <t>0.41*</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.49**</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>[0.17]</t>
+          <t>[0.08]</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.42***</t>
+          <t>0.25***</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>sp_push_plan</t>
+          <t>ss_push_plan</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>0.45**</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>0.67***</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>0.57***</t>
-        </is>
-      </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>0.27</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>0.55***</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0.39*</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.81***</t>
+          <t>0.65***</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>[0.22]</t>
+          <t>[0.17]</t>
         </is>
       </c>
     </row>

--- a/Output/SelfVsPartnerReport.xlsx
+++ b/Output/SelfVsPartnerReport.xlsx
@@ -1,21 +1,231 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pascku\Repos\02TimeAndTiesControl\Output\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07279CA0-5C93-4A5A-B39F-9B984D3A57D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-22510" yWindow="760" windowWidth="22620" windowHeight="13500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="merged_wb" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+  <si>
+    <t>0.42***</t>
+  </si>
+  <si>
+    <t>0.80***</t>
+  </si>
+  <si>
+    <t>0.44***</t>
+  </si>
+  <si>
+    <t>0.64***</t>
+  </si>
+  <si>
+    <t>0.25***</t>
+  </si>
+  <si>
+    <t>0.65***</t>
+  </si>
+  <si>
+    <t>Persuasion</t>
+  </si>
+  <si>
+    <t>Pressure</t>
+  </si>
+  <si>
+    <t>Plan-related pushing</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>ρ</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>within</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>ρ</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>between</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>ω</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">within </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>ω</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>between</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">0.48 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>[0.45, 0.51]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">0.33 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>[0.28, 0.37]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">0.31 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>[0.24, 0.38]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">0.99 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>[0.99,1.00]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">0.99 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>[0.99, 1.00]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1.00 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>[1.00, 1.00]</t>
+    </r>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -26,10 +236,42 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <vertAlign val="subscript"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Aptos"/>
       <family val="2"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +282,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -48,14 +290,53 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -63,13 +344,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -107,7 +396,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -141,6 +430,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -175,9 +465,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -350,270 +641,84 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="18.1328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="8.73046875" style="7" customWidth="1"/>
+    <col min="4" max="5" width="16.73046875" style="7" customWidth="1"/>
+    <col min="6" max="16384" width="9.06640625" style="7"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>RowName</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>persuasion_partner</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>ss_psc_more</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>pressure_partner</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>ss_nsc_more</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>pushing_partner</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>ss_push_plan</t>
-        </is>
+    <row r="1" spans="1:5" s="5" customFormat="1" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A1" s="1"/>
+      <c r="B1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>persuasion_partner</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>[0.20]</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>0.42***</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>0.21***</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0.23***</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0.40***</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0.18***</t>
-        </is>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>ss_psc_more</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>0.80***</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>[0.18]</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>0.13***</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0.33***</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0.30***</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0.45***</t>
-        </is>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>17</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>pressure_partner</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>0.30</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>0.29</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>[0.55]</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0.44***</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0.28***</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0.13***</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>ss_nsc_more</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>0.53***</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>0.54***</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>0.64***</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>[0.51]</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0.25***</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0.33***</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>pushing_partner</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>0.62***</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>0.67***</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>0.41*</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0.49**</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>[0.08]</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0.25***</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>ss_push_plan</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>0.45**</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>0.67***</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>0.27</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0.55***</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>0.65***</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>[0.17]</t>
-        </is>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A4" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>